--- a/manuscript/Table-1.xlsx
+++ b/manuscript/Table-1.xlsx
@@ -627,7 +627,7 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>Combination 2 and 3</t>
+          <t>Combination 2–3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -644,7 +644,7 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>Combination of 1, 2 and 3</t>
+          <t>Combination 1–2–3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -830,7 +830,7 @@
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>Opaque green to silvery gray</t>
+          <t>Dull green to silvery grey</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -923,7 +923,7 @@
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pale yellow with mottling or colored stripes</t>
+          <t>Pale yellow with mottling or stripes</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>Golden or deep yellow</t>
+          <t>Golden yellow</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dark purple</t>
+          <t>Morado oscuro</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kidney-shaped</t>
+          <t>Reniform</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cuboid</t>
+          <t>Cubic</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Wing color</t>
+          <t>Wing petal color</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1422,7 +1422,7 @@
     <row r="46">
       <c r="B46" t="inlineStr">
         <is>
-          <t>White with lilac border</t>
+          <t>White with lilac margin</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1456,7 +1456,7 @@
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dark lilac with violet spots</t>
+          <t>Lila oscuro con manchas violA!cias</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1524,7 +1524,7 @@
     <row r="52">
       <c r="B52" t="inlineStr">
         <is>
-          <t>White with lilac streaks</t>
+          <t>White with lilac veins</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1583,7 +1583,7 @@
     <row r="54">
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bicolored mottled</t>
+          <t>Bicoloured mottled</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1668,7 +1668,7 @@
     <row r="59">
       <c r="B59" t="inlineStr">
         <is>
-          <t>Wide stripes</t>
+          <t>Broad stripes</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1685,12 +1685,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Dark seed coat color</t>
+          <t>Darker seed coat color</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Yellow to greenish</t>
+          <t>Amarillo a verdoso</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1727,7 +1727,7 @@
     <row r="61">
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sulfur yellow</t>
+          <t>Amarrillo Asufrado</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1744,7 +1744,7 @@
     <row r="62">
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pure white</t>
+          <t>Blanco puro</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="63">
       <c r="B63" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Cafe</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1778,7 +1778,7 @@
     <row r="64">
       <c r="B64" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Grey</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1795,7 +1795,7 @@
     <row r="65">
       <c r="B65" t="inlineStr">
         <is>
-          <t>Brown, light to dark</t>
+          <t>Light to dark brown</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1931,7 +1931,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Light seed coat color</t>
+          <t>Lighter seed coat color</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2007,7 +2007,7 @@
     <row r="76">
       <c r="B76" t="inlineStr">
         <is>
-          <t>Light brown</t>
+          <t>Light coffee brown</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2024,7 +2024,7 @@
     <row r="77">
       <c r="B77" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Grey</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">

--- a/manuscript/Table-1.xlsx
+++ b/manuscript/Table-1.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -409,7 +409,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -424,7 +424,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -434,7 +434,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.13</t>
         </is>
       </c>
     </row>
@@ -502,12 +502,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -517,17 +517,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.73</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.13</t>
         </is>
       </c>
     </row>
@@ -573,12 +573,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.78</t>
         </is>
       </c>
     </row>
@@ -595,12 +595,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -610,17 +610,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.28</t>
         </is>
       </c>
     </row>
@@ -649,12 +649,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.94</t>
         </is>
       </c>
     </row>
@@ -671,12 +671,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
     </row>
@@ -708,12 +708,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.69</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.12</t>
         </is>
       </c>
     </row>
@@ -762,17 +762,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.24</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.14</t>
         </is>
       </c>
     </row>
@@ -818,12 +818,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.51</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.10</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.12</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.15</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.12</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.32</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.05</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.10</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.19</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.64</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.14</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.32</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.32</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.40</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.19</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1566,17 +1566,17 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.21</t>
         </is>
       </c>
     </row>
@@ -1656,12 +1656,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.36</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.99</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
     </row>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.06</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
     </row>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.13</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.34</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.16</t>
         </is>
       </c>
     </row>
@@ -1941,22 +1941,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.92</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.21</t>
         </is>
       </c>
     </row>
@@ -2012,12 +2012,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.17</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.08</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.14</t>
         </is>
       </c>
     </row>
@@ -2092,61 +2092,44 @@
     <row r="81">
       <c r="B81" t="inlineStr">
         <is>
-          <t>Light violet</t>
+          <t>Dark violet</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Dark violet</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>Mean ± SE</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>5.79 ± 0.77</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>3.08 ± 0.37</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>5.71 ± 0.74</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>3.10 ± 0.37</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
         <is>
           <t>0.61 ± 0.05</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>1.22 ± 0.12</t>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>1.23 ± 0.12</t>
         </is>
       </c>
     </row>

--- a/manuscript/Table-1.xlsx
+++ b/manuscript/Table-1.xlsx
@@ -14,12 +14,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="232">
   <si>
     <t>Qualitative trait</t>
   </si>
   <si>
-    <t>n (accessions)</t>
+    <t>Phenotypic classes observed</t>
+  </si>
+  <si>
+    <t>Na</t>
+  </si>
+  <si>
+    <t>fi</t>
   </si>
   <si>
     <t>Nc</t>
@@ -43,7 +49,13 @@
     <t>Emergent cotyledon color</t>
   </si>
   <si>
-    <t>78</t>
+    <t>Purple</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>0.46</t>
   </si>
   <si>
     <t>4</t>
@@ -64,9 +76,45 @@
     <t>0.90–1.14</t>
   </si>
   <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0.01</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>0.40</t>
+  </si>
+  <si>
+    <t>Very pale green</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>0.13</t>
+  </si>
+  <si>
     <t>Growth habit</t>
   </si>
   <si>
+    <t>Determinate bush</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>0.04</t>
+  </si>
+  <si>
     <t>1.58</t>
   </si>
   <si>
@@ -82,10 +130,34 @@
     <t>0.49–0.92</t>
   </si>
   <si>
+    <t>Indeterminate bush</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>Indeterminate prostrate</t>
+  </si>
+  <si>
+    <t>Indeterminate climbing</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>0.78</t>
+  </si>
+  <si>
     <t>Pod position at 50% physiological maturity</t>
   </si>
   <si>
-    <t>3</t>
+    <t>Center</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>0.03</t>
   </si>
   <si>
     <t>1.14</t>
@@ -103,9 +175,30 @@
     <t>0.07–0.46</t>
   </si>
   <si>
+    <t>Combination 1–2–3</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>0.94</t>
+  </si>
+  <si>
+    <t>Combination 2–3</t>
+  </si>
+  <si>
     <t>Pod curvature at 50% physiological maturity</t>
   </si>
   <si>
+    <t>Straight</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>0.12</t>
+  </si>
+  <si>
     <t>1.89</t>
   </si>
   <si>
@@ -121,9 +214,36 @@
     <t>0.63–0.95</t>
   </si>
   <si>
+    <t>Slightly curved</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>0.69</t>
+  </si>
+  <si>
+    <t>Curved</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>0.19</t>
+  </si>
+  <si>
     <t>Pod color at the onset of physiological maturity</t>
   </si>
   <si>
+    <t>Purple stripe on green</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>0.24</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
@@ -142,9 +262,45 @@
     <t>1.05–1.35</t>
   </si>
   <si>
+    <t>Pale red stripe on green</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>0.09</t>
+  </si>
+  <si>
+    <t>Normal green</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>0.51</t>
+  </si>
+  <si>
+    <t>Bright green</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>0.14</t>
+  </si>
+  <si>
+    <t>Dull green to silvery grey</t>
+  </si>
+  <si>
     <t>Pod color at 90% physiological maturity</t>
   </si>
   <si>
+    <t>Dark purple</t>
+  </si>
+  <si>
+    <t>0.06</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
@@ -163,9 +319,45 @@
     <t>1.41–1.70</t>
   </si>
   <si>
+    <t>Yellow</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>Pale yellow with mottling or stripes</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>Pale yellow</t>
+  </si>
+  <si>
+    <t>Yellow with red pigment</t>
+  </si>
+  <si>
+    <t>Yellow with purple pigment</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>0.10</t>
+  </si>
+  <si>
     <t>Leaf persistence</t>
   </si>
   <si>
+    <t>All leaves fallen</t>
+  </si>
+  <si>
     <t>2.30</t>
   </si>
   <si>
@@ -181,6 +373,24 @@
     <t>0.80–1.03</t>
   </si>
   <si>
+    <t>Intermediate</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>0.56</t>
+  </si>
+  <si>
+    <t>All leaves persistent</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>0.32</t>
+  </si>
+  <si>
     <t>Dry pod color</t>
   </si>
   <si>
@@ -199,9 +409,36 @@
     <t>0.81–1.22</t>
   </si>
   <si>
+    <t>Golden yellow</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>0.64</t>
+  </si>
+  <si>
+    <t>Pale yellow to white</t>
+  </si>
+  <si>
+    <t>Cream with purple pigment</t>
+  </si>
+  <si>
+    <t>Beige</t>
+  </si>
+  <si>
     <t>Seed shape</t>
   </si>
   <si>
+    <t>Round</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>0.26</t>
+  </si>
+  <si>
     <t>4.09</t>
   </si>
   <si>
@@ -217,9 +454,36 @@
     <t>1.33–1.54</t>
   </si>
   <si>
+    <t>Oval</t>
+  </si>
+  <si>
+    <t>Cuboid</t>
+  </si>
+  <si>
+    <t>Reniform</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>0.23</t>
+  </si>
+  <si>
+    <t>Truncate fastigiate</t>
+  </si>
+  <si>
     <t>Wing petal color at 90% flowering</t>
   </si>
   <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>0.18</t>
+  </si>
+  <si>
     <t>2.87</t>
   </si>
   <si>
@@ -235,12 +499,15 @@
     <t>1.00–1.29</t>
   </si>
   <si>
+    <t>Lilac</t>
+  </si>
+  <si>
+    <t>Light lilac</t>
+  </si>
+  <si>
     <t>Standard petal color at 90% flowering</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>0.65 ± 0.05</t>
   </si>
   <si>
@@ -253,13 +520,34 @@
     <t>1.12–1.56</t>
   </si>
   <si>
+    <t>White with lilac margin</t>
+  </si>
+  <si>
+    <t>Dark lilac with violet spots</t>
+  </si>
+  <si>
+    <t>Carmine red</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>0.54</t>
+  </si>
+  <si>
+    <t>White with lilac veins</t>
+  </si>
+  <si>
     <t>Seed coat pattern</t>
   </si>
   <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>7</t>
+    <t>Absent</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>0.29</t>
   </si>
   <si>
     <t>3.80</t>
@@ -277,9 +565,48 @@
     <t>1.29–1.64</t>
   </si>
   <si>
+    <t>Constant mottling</t>
+  </si>
+  <si>
+    <t>Striped</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>0.36</t>
+  </si>
+  <si>
+    <t>Rhomboid mottling</t>
+  </si>
+  <si>
+    <t>Mottled</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>0.21</t>
+  </si>
+  <si>
+    <t>Broad stripes</t>
+  </si>
+  <si>
+    <t>Bicolour mottled</t>
+  </si>
+  <si>
     <t>Lighter seed coat color</t>
   </si>
   <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>0.34</t>
+  </si>
+  <si>
     <t>13</t>
   </si>
   <si>
@@ -298,10 +625,46 @@
     <t>1.67–2.12</t>
   </si>
   <si>
+    <t>Light to dark brown</t>
+  </si>
+  <si>
+    <t>Brown</t>
+  </si>
+  <si>
+    <t>Yellow to greenish</t>
+  </si>
+  <si>
+    <t>Pure white</t>
+  </si>
+  <si>
+    <t>0.16</t>
+  </si>
+  <si>
+    <t>Pink</t>
+  </si>
+  <si>
+    <t>Sulfur yellow</t>
+  </si>
+  <si>
+    <t>Grey</t>
+  </si>
+  <si>
+    <t>Red to purple</t>
+  </si>
+  <si>
+    <t>Dark brown</t>
+  </si>
+  <si>
+    <t>Orange</t>
+  </si>
+  <si>
     <t>Darker seed coat color</t>
   </si>
   <si>
-    <t>9</t>
+    <t>Light brown</t>
+  </si>
+  <si>
+    <t>0.17</t>
   </si>
   <si>
     <t>5.84</t>
@@ -319,7 +682,16 @@
     <t>1.70–2.01</t>
   </si>
   <si>
-    <t>Mean ± SE (across traits)</t>
+    <t>Dark violet</t>
+  </si>
+  <si>
+    <t>0.08</t>
+  </si>
+  <si>
+    <t>Whitish</t>
+  </si>
+  <si>
+    <t>Mean ± SE</t>
   </si>
   <si>
     <t>5.71 ± 0.74</t>
@@ -331,7 +703,13 @@
     <t>0.61 ± 0.05</t>
   </si>
   <si>
+    <t>0.50–0.72</t>
+  </si>
+  <si>
     <t>1.23 ± 0.12</t>
+  </si>
+  <si>
+    <t>0.96–1.50</t>
   </si>
 </sst>
 </file>
@@ -674,10 +1052,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1">
+    <row r="1" spans="1:10" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -702,386 +1080,1208 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H13" t="s">
+        <v>63</v>
+      </c>
+      <c r="I13" t="s">
+        <v>64</v>
+      </c>
+      <c r="J13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" t="s">
+        <v>79</v>
+      </c>
+      <c r="I16" t="s">
+        <v>80</v>
+      </c>
+      <c r="J16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="B17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="B18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="B19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="B20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>92</v>
+      </c>
+      <c r="B21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" t="s">
+        <v>94</v>
+      </c>
+      <c r="E21" t="s">
+        <v>95</v>
+      </c>
+      <c r="F21" t="s">
+        <v>96</v>
+      </c>
+      <c r="G21" t="s">
+        <v>97</v>
+      </c>
+      <c r="H21" t="s">
+        <v>98</v>
+      </c>
+      <c r="I21" t="s">
+        <v>99</v>
+      </c>
+      <c r="J21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="B22" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="B23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C23" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="B24" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" t="s">
+        <v>105</v>
+      </c>
+      <c r="D24" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="B25" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="B26" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" t="s">
+        <v>110</v>
+      </c>
+      <c r="D26" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" t="s">
+        <v>112</v>
+      </c>
+      <c r="B27" t="s">
+        <v>113</v>
+      </c>
+      <c r="C27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" t="s">
+        <v>114</v>
+      </c>
+      <c r="G27" t="s">
+        <v>115</v>
+      </c>
+      <c r="H27" t="s">
+        <v>116</v>
+      </c>
+      <c r="I27" t="s">
+        <v>117</v>
+      </c>
+      <c r="J27" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="B28" t="s">
+        <v>119</v>
+      </c>
+      <c r="C28" t="s">
+        <v>120</v>
+      </c>
+      <c r="D28" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="B29" t="s">
+        <v>122</v>
+      </c>
+      <c r="C29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D29" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" t="s">
+        <v>125</v>
+      </c>
+      <c r="B30" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" t="s">
+        <v>47</v>
+      </c>
+      <c r="E30" t="s">
+        <v>76</v>
+      </c>
+      <c r="F30" t="s">
+        <v>126</v>
+      </c>
+      <c r="G30" t="s">
+        <v>127</v>
+      </c>
+      <c r="H30" t="s">
+        <v>128</v>
+      </c>
+      <c r="I30" t="s">
+        <v>129</v>
+      </c>
+      <c r="J30" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="B31" t="s">
+        <v>131</v>
+      </c>
+      <c r="C31" t="s">
+        <v>132</v>
+      </c>
+      <c r="D31" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="B32" t="s">
+        <v>134</v>
+      </c>
+      <c r="C32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="B33" t="s">
+        <v>135</v>
+      </c>
+      <c r="C33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="B34" t="s">
+        <v>136</v>
+      </c>
+      <c r="C34" t="s">
+        <v>110</v>
+      </c>
+      <c r="D34" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" t="s">
+        <v>137</v>
+      </c>
+      <c r="B35" t="s">
+        <v>138</v>
+      </c>
+      <c r="C35" t="s">
+        <v>139</v>
+      </c>
+      <c r="D35" t="s">
+        <v>140</v>
+      </c>
+      <c r="E35" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35" t="s">
+        <v>141</v>
+      </c>
+      <c r="G35" t="s">
+        <v>142</v>
+      </c>
+      <c r="H35" t="s">
+        <v>143</v>
+      </c>
+      <c r="I35" t="s">
+        <v>144</v>
+      </c>
+      <c r="J35" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="B36" t="s">
+        <v>146</v>
+      </c>
+      <c r="C36" t="s">
+        <v>123</v>
+      </c>
+      <c r="D36" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="B37" t="s">
+        <v>147</v>
+      </c>
+      <c r="C37" t="s">
+        <v>89</v>
+      </c>
+      <c r="D37" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="B38" t="s">
+        <v>148</v>
+      </c>
+      <c r="C38" t="s">
+        <v>149</v>
+      </c>
+      <c r="D38" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="B39" t="s">
+        <v>151</v>
+      </c>
+      <c r="C39" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" t="s">
+        <v>152</v>
+      </c>
+      <c r="B40" t="s">
+        <v>153</v>
+      </c>
+      <c r="C40" t="s">
+        <v>154</v>
+      </c>
+      <c r="D40" t="s">
+        <v>155</v>
+      </c>
+      <c r="E40" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" t="s">
+        <v>156</v>
+      </c>
+      <c r="G40" t="s">
+        <v>157</v>
+      </c>
+      <c r="H40" t="s">
+        <v>158</v>
+      </c>
+      <c r="I40" t="s">
+        <v>159</v>
+      </c>
+      <c r="J40" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="B41" t="s">
+        <v>161</v>
+      </c>
+      <c r="C41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="B42" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="C42" t="s">
+        <v>21</v>
+      </c>
+      <c r="D42" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="B43" t="s">
+        <v>162</v>
+      </c>
+      <c r="C43" t="s">
+        <v>123</v>
+      </c>
+      <c r="D43" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="B44" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" t="s">
+        <v>46</v>
+      </c>
+      <c r="D44" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" t="s">
+        <v>163</v>
+      </c>
+      <c r="B45" t="s">
+        <v>153</v>
+      </c>
+      <c r="C45" t="s">
+        <v>27</v>
+      </c>
+      <c r="D45" t="s">
+        <v>28</v>
+      </c>
+      <c r="E45" t="s">
+        <v>110</v>
+      </c>
+      <c r="F45" t="s">
+        <v>156</v>
+      </c>
+      <c r="G45" t="s">
+        <v>164</v>
+      </c>
+      <c r="H45" t="s">
+        <v>165</v>
+      </c>
+      <c r="I45" t="s">
+        <v>166</v>
+      </c>
+      <c r="J45" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="B46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C46" t="s">
+        <v>31</v>
+      </c>
+      <c r="D46" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="B47" t="s">
+        <v>161</v>
+      </c>
+      <c r="C47" t="s">
+        <v>70</v>
+      </c>
+      <c r="D47" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="B48" t="s">
+        <v>168</v>
+      </c>
+      <c r="C48" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="D48" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="B49" t="s">
+        <v>169</v>
+      </c>
+      <c r="C49" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="B50" t="s">
+        <v>170</v>
+      </c>
+      <c r="C50" t="s">
+        <v>46</v>
+      </c>
+      <c r="D50" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="B51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" t="s">
+        <v>171</v>
+      </c>
+      <c r="D51" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="B52" t="s">
+        <v>173</v>
+      </c>
+      <c r="C52" t="s">
+        <v>21</v>
+      </c>
+      <c r="D52" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" t="s">
+        <v>174</v>
+      </c>
+      <c r="B53" t="s">
+        <v>175</v>
+      </c>
+      <c r="C53" t="s">
+        <v>176</v>
+      </c>
+      <c r="D53" t="s">
+        <v>177</v>
+      </c>
+      <c r="E53" t="s">
+        <v>83</v>
+      </c>
+      <c r="F53" t="s">
+        <v>178</v>
+      </c>
+      <c r="G53" t="s">
+        <v>179</v>
+      </c>
+      <c r="H53" t="s">
+        <v>180</v>
+      </c>
+      <c r="I53" t="s">
+        <v>181</v>
+      </c>
+      <c r="J53" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="B54" t="s">
+        <v>183</v>
+      </c>
+      <c r="C54" t="s">
+        <v>31</v>
+      </c>
+      <c r="D54" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="B55" t="s">
+        <v>184</v>
+      </c>
+      <c r="C55" t="s">
+        <v>185</v>
+      </c>
+      <c r="D55" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="B56" t="s">
+        <v>187</v>
+      </c>
+      <c r="C56" t="s">
+        <v>21</v>
+      </c>
+      <c r="D56" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="B57" t="s">
+        <v>188</v>
+      </c>
+      <c r="C57" t="s">
+        <v>189</v>
+      </c>
+      <c r="D57" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="B58" t="s">
+        <v>191</v>
+      </c>
+      <c r="C58" t="s">
+        <v>14</v>
+      </c>
+      <c r="D58" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="B59" t="s">
+        <v>192</v>
+      </c>
+      <c r="C59" t="s">
+        <v>31</v>
+      </c>
+      <c r="D59" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" t="s">
+        <v>193</v>
+      </c>
+      <c r="B60" t="s">
+        <v>194</v>
+      </c>
+      <c r="C60" t="s">
+        <v>195</v>
+      </c>
+      <c r="D60" t="s">
+        <v>196</v>
+      </c>
+      <c r="E60" t="s">
+        <v>197</v>
+      </c>
+      <c r="F60" t="s">
+        <v>198</v>
+      </c>
+      <c r="G60" t="s">
+        <v>199</v>
+      </c>
+      <c r="H60" t="s">
+        <v>200</v>
+      </c>
+      <c r="I60" t="s">
+        <v>201</v>
+      </c>
+      <c r="J60" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="B61" t="s">
+        <v>203</v>
+      </c>
+      <c r="C61" t="s">
+        <v>76</v>
+      </c>
+      <c r="D61" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="B62" t="s">
+        <v>204</v>
+      </c>
+      <c r="C62" t="s">
+        <v>21</v>
+      </c>
+      <c r="D62" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="B63" t="s">
+        <v>205</v>
+      </c>
+      <c r="C63" t="s">
+        <v>21</v>
+      </c>
+      <c r="D63" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="B64" t="s">
+        <v>206</v>
+      </c>
+      <c r="C64" t="s">
+        <v>46</v>
+      </c>
+      <c r="D64" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="B65" t="s">
         <v>20</v>
       </c>
-      <c r="H3" t="s">
+      <c r="C65" t="s">
+        <v>105</v>
+      </c>
+      <c r="D65" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="B66" t="s">
+        <v>208</v>
+      </c>
+      <c r="C66" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
+      <c r="D66" t="s">
         <v>22</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" t="s">
+    </row>
+    <row r="67" spans="1:10">
+      <c r="B67" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" t="s">
         <v>27</v>
       </c>
-      <c r="H4" t="s">
+      <c r="D67" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
+    <row r="68" spans="1:10">
+      <c r="B68" t="s">
+        <v>209</v>
+      </c>
+      <c r="C68" t="s">
+        <v>21</v>
+      </c>
+      <c r="D68" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="B69" t="s">
+        <v>210</v>
+      </c>
+      <c r="C69" t="s">
         <v>31</v>
       </c>
-      <c r="F5" t="s">
+      <c r="D69" t="s">
         <v>32</v>
       </c>
-      <c r="G5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" t="s">
+    </row>
+    <row r="70" spans="1:10">
+      <c r="B70" t="s">
+        <v>211</v>
+      </c>
+      <c r="C70" t="s">
+        <v>105</v>
+      </c>
+      <c r="D70" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="B71" t="s">
+        <v>212</v>
+      </c>
+      <c r="C71" t="s">
+        <v>46</v>
+      </c>
+      <c r="D71" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="B72" t="s">
+        <v>213</v>
+      </c>
+      <c r="C72" t="s">
+        <v>21</v>
+      </c>
+      <c r="D72" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" t="s">
+        <v>214</v>
+      </c>
+      <c r="B73" t="s">
+        <v>215</v>
+      </c>
+      <c r="C73" t="s">
+        <v>197</v>
+      </c>
+      <c r="D73" t="s">
+        <v>216</v>
+      </c>
+      <c r="E73" t="s">
+        <v>59</v>
+      </c>
+      <c r="F73" t="s">
+        <v>217</v>
+      </c>
+      <c r="G73" t="s">
+        <v>218</v>
+      </c>
+      <c r="H73" t="s">
+        <v>219</v>
+      </c>
+      <c r="I73" t="s">
+        <v>220</v>
+      </c>
+      <c r="J73" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="B74" t="s">
+        <v>213</v>
+      </c>
+      <c r="C74" t="s">
+        <v>89</v>
+      </c>
+      <c r="D74" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="B75" t="s">
+        <v>153</v>
+      </c>
+      <c r="C75" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75" t="s">
         <v>39</v>
       </c>
-      <c r="G6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" t="s">
+    </row>
+    <row r="76" spans="1:10">
+      <c r="B76" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" t="s">
         <v>46</v>
       </c>
-      <c r="G7" t="s">
+      <c r="D76" t="s">
         <v>47</v>
       </c>
-      <c r="H7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" t="s">
-        <v>59</v>
-      </c>
-      <c r="H9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E10" t="s">
-        <v>63</v>
-      </c>
-      <c r="F10" t="s">
-        <v>64</v>
-      </c>
-      <c r="G10" t="s">
-        <v>65</v>
-      </c>
-      <c r="H10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>68</v>
-      </c>
-      <c r="E11" t="s">
-        <v>69</v>
-      </c>
-      <c r="F11" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" t="s">
-        <v>71</v>
-      </c>
-      <c r="H11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F12" t="s">
-        <v>76</v>
-      </c>
-      <c r="G12" t="s">
-        <v>77</v>
-      </c>
-      <c r="H12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" t="s">
-        <v>83</v>
-      </c>
-      <c r="F13" t="s">
-        <v>84</v>
-      </c>
-      <c r="G13" t="s">
-        <v>85</v>
-      </c>
-      <c r="H13" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" t="s">
-        <v>87</v>
-      </c>
-      <c r="B14" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" t="s">
-        <v>89</v>
-      </c>
-      <c r="E14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F14" t="s">
-        <v>91</v>
-      </c>
-      <c r="G14" t="s">
-        <v>92</v>
-      </c>
-      <c r="H14" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" t="s">
-        <v>94</v>
-      </c>
-      <c r="B15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="77" spans="1:10">
+      <c r="B77" t="s">
+        <v>222</v>
+      </c>
+      <c r="C77" t="s">
+        <v>46</v>
+      </c>
+      <c r="D77" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="B78" t="s">
+        <v>175</v>
+      </c>
+      <c r="C78" t="s">
+        <v>139</v>
+      </c>
+      <c r="D78" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="B79" t="s">
+        <v>208</v>
+      </c>
+      <c r="C79" t="s">
+        <v>31</v>
+      </c>
+      <c r="D79" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="B80" t="s">
+        <v>210</v>
+      </c>
+      <c r="C80" t="s">
         <v>95</v>
       </c>
-      <c r="D15" t="s">
-        <v>96</v>
-      </c>
-      <c r="E15" t="s">
-        <v>97</v>
-      </c>
-      <c r="F15" t="s">
-        <v>98</v>
-      </c>
-      <c r="G15" t="s">
-        <v>99</v>
-      </c>
-      <c r="H15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" t="s">
-        <v>101</v>
-      </c>
-      <c r="C16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E16" t="s">
-        <v>104</v>
-      </c>
-      <c r="G16" t="s">
-        <v>105</v>
+      <c r="D80" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="B81" t="s">
+        <v>224</v>
+      </c>
+      <c r="C81" t="s">
+        <v>189</v>
+      </c>
+      <c r="D81" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82" t="s">
+        <v>225</v>
+      </c>
+      <c r="E82" t="s">
+        <v>226</v>
+      </c>
+      <c r="F82" t="s">
+        <v>227</v>
+      </c>
+      <c r="G82" t="s">
+        <v>228</v>
+      </c>
+      <c r="H82" t="s">
+        <v>229</v>
+      </c>
+      <c r="I82" t="s">
+        <v>230</v>
+      </c>
+      <c r="J82" t="s">
+        <v>231</v>
       </c>
     </row>
   </sheetData>
